--- a/docs/Decodifiche/32_dec_comprensione_dichiarante.xlsx
+++ b/docs/Decodifiche/32_dec_comprensione_dichiarante.xlsx
@@ -59,46 +59,46 @@
     <t>Muto ma non sordo che sa scrivere</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Sordo ma non muto che non sa leggere</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Sordo ma non muto che sa leggere</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Sordomuto che non sa né leggere né scrivere</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Sordomuto che sa leggere e scrivere</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Sordomuto che sa leggere ma non può scrivere</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Sordomuto che sa leggere ma non sa scrivere</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
     <t>Persona che non conosce la lingua italiana</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Sordo ma non muto che non sa leggere</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Sordo ma non muto che sa leggere</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Sordomuto che non sa né leggere né scrivere</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Sordomuto che sa leggere e scrivere</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sordomuto che sa leggere ma non può scrivere</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Sordomuto che sa leggere ma non sa scrivere</t>
   </si>
 </sst>
 </file>
